--- a/data/employee_leave_data.xlsx
+++ b/data/employee_leave_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karth\Desktop\lms_rag_xl\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84035CFC-FE6D-4C9E-81C3-2B691406327B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9494EC-DDC4-4B1B-BE13-93DBFF3166A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3140" yWindow="3140" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3140" yWindow="3140" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
@@ -1144,6 +1144,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D70"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="25.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
